--- a/tests/workbooktests/workbooks/test_calibratedmodel.xlsx
+++ b/tests/workbooktests/workbooks/test_calibratedmodel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6889E0-1D68-47A0-8ACF-903534D570DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2799A090-5818-4643-B8ED-51009A415CB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" xr2:uid="{2FEFDE40-9C41-44A1-8868-8F33D5CA59CC}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -150,7 +139,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,7 +183,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -527,14 +516,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5801CCEB-5ED0-4426-BDA0-80040ADEB374}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="47.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -542,16 +531,16 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="e">
-        <f ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <f>_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -559,25 +548,25 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="e">
-        <f ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R6C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="e">
-        <f ca="1">_xll.qlFlatForward(B2,0.02)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <f>_xll.qlFlatForward(B2,0.02,"actual365fixed")</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R7C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -585,7 +574,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -593,7 +582,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -601,7 +590,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -609,7 +598,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -617,7 +606,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -625,52 +614,52 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="15">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B16" t="e">
-        <f ca="1">_xll.qlHestonProcess(B7,B6,B5,B10,B11,B12,B13,B14,B15,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="str">
+        <f>_xll.qlHestonProcess(B7,B6,B5,B10,B11,B12,B13,B14,B15,B2)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R16C2HestonProcess,A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="e">
-        <f ca="1">_xll.qlHestonModel(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="str">
+        <f>_xll.qlHestonModel(B16)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R18C2HestonModel,A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="e">
-        <f ca="1">_xll.qlAnalyticHestonEngine(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="str">
+        <f>_xll.qlAnalyticHestonEngine(B18)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R19C2AnalyticHestonEngine,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" t="e">
-        <f ca="1">_xll.qlLevenbergMarquardt(,,,,B19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="str">
+        <f>_xll.qlLevenbergMarquardt(,,,,B19)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R21C2LevenbergMarquardt,A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" t="e">
-        <f ca="1">_xll.qlEndCriteria(100,10,0.000001,0.000001,0.000001,B21)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="str">
+        <f>_xll.qlEndCriteria(100,10,0.000001,0.000001,0.000001,B21)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R22C2EndCriteria,A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -678,7 +667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="C26" t="s">
         <v>17</v>
       </c>
@@ -689,14 +678,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="e">
-        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B27,$B$19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B27" t="e">
-        <f ca="1">_xll.qlHestonModelHelper(C27,$B$24,$B$5,D27,E27,$B$7,$B$6)</f>
-        <v>#VALUE!</v>
+    <row r="27" spans="1:5">
+      <c r="A27" t="b">
+        <f>_xll.qlBlackCalibrationHelperSetPricingEngine(B27,$B$19)</f>
+        <v>1</v>
+      </c>
+      <c r="B27" t="str">
+        <f>_xll.qlHestonModelHelper(C27,$B$24,$B$5,D27,E27,$B$7,$B$6)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R27C2HestonModelHelper,A</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -708,14 +697,14 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="e">
-        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B28,$B$19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B28" t="e">
-        <f ca="1">_xll.qlHestonModelHelper(C28,$B$24,$B$5,D28,E28,$B$7,$B$6)</f>
-        <v>#VALUE!</v>
+    <row r="28" spans="1:5">
+      <c r="A28" t="b">
+        <f>_xll.qlBlackCalibrationHelperSetPricingEngine(B28,$B$19)</f>
+        <v>1</v>
+      </c>
+      <c r="B28" t="str">
+        <f>_xll.qlHestonModelHelper(C28,$B$24,$B$5,D28,E28,$B$7,$B$6)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R28C2HestonModelHelper,A</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
@@ -727,14 +716,14 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="e">
-        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B29,$B$19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B29" t="e">
-        <f ca="1">_xll.qlHestonModelHelper(C29,$B$24,$B$5,D29,E29,$B$7,$B$6)</f>
-        <v>#VALUE!</v>
+    <row r="29" spans="1:5">
+      <c r="A29" t="b">
+        <f>_xll.qlBlackCalibrationHelperSetPricingEngine(B29,$B$19)</f>
+        <v>1</v>
+      </c>
+      <c r="B29" t="str">
+        <f>_xll.qlHestonModelHelper(C29,$B$24,$B$5,D29,E29,$B$7,$B$6)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R29C2HestonModelHelper,A</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -746,14 +735,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="e">
-        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B30,$B$19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B30" t="e">
-        <f ca="1">_xll.qlHestonModelHelper(C30,$B$24,$B$5,D30,E30,$B$7,$B$6)</f>
-        <v>#VALUE!</v>
+    <row r="30" spans="1:5">
+      <c r="A30" t="b">
+        <f>_xll.qlBlackCalibrationHelperSetPricingEngine(B30,$B$19)</f>
+        <v>1</v>
+      </c>
+      <c r="B30" t="str">
+        <f>_xll.qlHestonModelHelper(C30,$B$24,$B$5,D30,E30,$B$7,$B$6)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R30C2HestonModelHelper,A</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
@@ -765,14 +754,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="e">
-        <f ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B31,$B$19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B31" t="e">
-        <f ca="1">_xll.qlHestonModelHelper(C31,$B$24,$B$5,D31,E31,$B$7,$B$6)</f>
-        <v>#VALUE!</v>
+    <row r="31" spans="1:5">
+      <c r="A31" t="b">
+        <f>_xll.qlBlackCalibrationHelperSetPricingEngine(B31,$B$19)</f>
+        <v>1</v>
+      </c>
+      <c r="B31" t="str">
+        <f>_xll.qlHestonModelHelper(C31,$B$24,$B$5,D31,E31,$B$7,$B$6)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R31C2HestonModelHelper,A</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
@@ -784,92 +773,92 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="B33" t="e">
-        <f ca="1">_xll.qlCalibratedModelCalibrate(B18,B27:B31,B21,B22,,,,A27:A31)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B33" t="b">
+        <f>_xll.qlCalibratedModelCalibrate(B18,B27:B31,B21,B22,,,,A27:A31)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>23</v>
       </c>
-      <c r="B36" t="e">
-        <f ca="1">_xll.qlCalibratedModelParams(B18,B33)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D36" t="e">
-        <f ca="1">_xll.qlHestonModelTheta(B18,B33)</f>
-        <v>#VALUE!</v>
+      <c r="B36">
+        <f>_xll.qlCalibratedModelParams(B18,B33)</f>
+        <v>7.6079676974909846E-2</v>
+      </c>
+      <c r="D36">
+        <f>_xll.qlHestonModelTheta(B18,B33)</f>
+        <v>7.6079676974909846E-2</v>
       </c>
       <c r="E36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D37" t="e">
-        <f ca="1">_xll.qlHestonModelKappa(B18,B33)</f>
-        <v>#VALUE!</v>
+    <row r="37" spans="1:5">
+      <c r="D37">
+        <f>_xll.qlHestonModelKappa(B18,B33)</f>
+        <v>0.39860603531956362</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D38" t="e">
-        <f ca="1">_xll.qlHestonModelSigma(B18,B33)</f>
-        <v>#VALUE!</v>
+    <row r="38" spans="1:5">
+      <c r="D38">
+        <f>_xll.qlHestonModelSigma(B18,B33)</f>
+        <v>1.3966173286805368</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D39" t="e">
-        <f ca="1">_xll.qlHestonModelRho(B18,B33)</f>
-        <v>#VALUE!</v>
+    <row r="39" spans="1:5">
+      <c r="D39">
+        <f>_xll.qlHestonModelRho(B18,B33)</f>
+        <v>-0.35064473072253466</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D40" t="e">
-        <f ca="1">_xll.qlHestonModelV0(B18,B33)</f>
-        <v>#VALUE!</v>
+    <row r="40" spans="1:5">
+      <c r="D40">
+        <f>_xll.qlHestonModelV0(B18,B33)</f>
+        <v>0.19563086807319552</v>
       </c>
       <c r="E40" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>24</v>
       </c>
-      <c r="B42" t="e">
-        <f ca="1">_xll.qlCalibratedModelProblemValues(B18,B33)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <f>_xll.qlCalibratedModelProblemValues(B18,B33)</f>
+        <v>3.4636638507032998E-5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>25</v>
       </c>
-      <c r="B48" t="e">
-        <f ca="1">_xll.qlCalibratedModelProblemValuesFunctionEvaluation(B18,B33)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <f>_xll.qlCalibratedModelProblemValuesFunctionEvaluation(B18,B33)</f>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>26</v>
       </c>
-      <c r="B50" t="e">
-        <f ca="1">_xll.qlCalibratedModelHandle(B18)</f>
-        <v>#VALUE!</v>
+      <c r="B50" t="str">
+        <f>_xll.qlCalibratedModelHandle(B18)</f>
+        <v>欣[test_calibratedmodel.xlsx]Sheet1!R50C2CalibratedModelHandle,A</v>
       </c>
     </row>
   </sheetData>
